--- a/data/trans_bre/P32A-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P32A-Clase-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 0,0</t>
+          <t>-1,86; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 0,58</t>
+          <t>-3,43; 0,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 5,11</t>
+          <t>-1,07; 4,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 1,67</t>
+          <t>-2,48; 1,87</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,17 +685,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 455,57</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 224,37</t>
+          <t>-100,0; 251,92</t>
         </is>
       </c>
     </row>
@@ -765,17 +765,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 1,33</t>
+          <t>-3,74; 1,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 4,43</t>
+          <t>-1,28; 3,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 3,85</t>
+          <t>-0,44; 4,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -790,12 +790,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 1115,95</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-84,54; 3181,04</t>
+          <t>-70,25; 3658,23</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,04; -0,52</t>
+          <t>-2,87; -0,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,14; -1,8</t>
+          <t>-6,18; -1,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 6,94</t>
+          <t>-2,88; 8,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,46; -0,75</t>
+          <t>-4,58; -0,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,59; -0,69</t>
+          <t>-2,66; -0,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 0,23</t>
+          <t>-3,1; 0,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,58; -0,11</t>
+          <t>-2,49; 0,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,75; -0,16</t>
+          <t>-3,92; -0,26</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -985,17 +985,17 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 62,31</t>
+          <t>-100,0; 81,84</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 47,63</t>
+          <t>-100,0; 120,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-98,62; -2,74</t>
+          <t>-98,13; -4,36</t>
         </is>
       </c>
     </row>
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 3,28</t>
+          <t>-1,45; 3,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 0,8</t>
+          <t>-4,18; 0,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,65; -0,89</t>
+          <t>-5,79; -0,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 2,32</t>
+          <t>-2,83; 2,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1085,17 +1085,17 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 116,19</t>
+          <t>-100,0; 101,03</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 35,41</t>
+          <t>-100,0; 55,78</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-78,21; 256,67</t>
+          <t>-81,33; 236,7</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,89</t>
+          <t>0,0; 2,33</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 0,98</t>
+          <t>-5,37; 1,45</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 2,24</t>
+          <t>-3,96; 1,99</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,41</t>
+          <t>0,0; 9,39</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-89,16; 300,93</t>
+          <t>-88,72; 336,25</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,38; -0,11</t>
+          <t>-1,37; -0,16</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,68; -0,76</t>
+          <t>-2,58; -0,7</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 0,35</t>
+          <t>-1,52; 0,46</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 0,46</t>
+          <t>-1,51; 0,57</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-92,17; 16,67</t>
+          <t>-100,0; 8,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-86,56; -30,37</t>
+          <t>-85,26; -27,96</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-67,2; 25,37</t>
+          <t>-64,18; 29,95</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-72,61; 32,12</t>
+          <t>-68,59; 40,44</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P32A-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P32A-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,49</t>
+          <t>-0,78</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-25,93%</t>
+          <t>-36,77%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 0,0</t>
+          <t>-1,62; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 0,78</t>
+          <t>-3,55; 0,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 4,95</t>
+          <t>-1,15; 5,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 1,87</t>
+          <t>-2,93; 1,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 455,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 251,92</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,24</t>
+          <t>1,67</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>149,75%</t>
+          <t>144,74%</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,78; -0,43</t>
+          <t>-4,17; -0,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 1,38</t>
+          <t>-3,98; 1,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 3,95</t>
+          <t>-1,38; 3,93</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 4,2</t>
+          <t>-0,71; 4,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -790,12 +790,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 1115,95</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-70,25; 3658,23</t>
+          <t>-69,21; —</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-1,99</t>
+          <t>-1,82</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,87; -0,51</t>
+          <t>-3,24; -0,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,18; -1,84</t>
+          <t>-6,13; -1,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 8,66</t>
+          <t>-2,97; 6,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,58; -0,76</t>
+          <t>-4,19; -0,7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 626,32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-1,58</t>
+          <t>0,74</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-69,68%</t>
+          <t>34,79%</t>
         </is>
       </c>
     </row>
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,66; -0,59</t>
+          <t>-2,55; -0,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 0,25</t>
+          <t>-3,33; 0,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 0,16</t>
+          <t>-2,56; 0,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,92; -0,26</t>
+          <t>-1,28; 5,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -985,17 +985,17 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 81,84</t>
+          <t>-100,0; 52,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 120,14</t>
+          <t>-100,0; 147,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-98,13; -4,36</t>
+          <t>-57,39; 426,04</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,28</t>
+          <t>-0,25</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-12,99%</t>
+          <t>-12,96%</t>
         </is>
       </c>
     </row>
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 3,2</t>
+          <t>-1,46; 3,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 0,78</t>
+          <t>-4,13; 0,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,79; -0,83</t>
+          <t>-5,51; -0,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 2,06</t>
+          <t>-2,22; 1,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1085,24 +1085,24 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 101,03</t>
+          <t>-100,0; 71,33</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 55,78</t>
+          <t>-100,0; 51,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-81,33; 236,7</t>
+          <t>-76,92; 226,12</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,83</t>
+          <t>1,76</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,33</t>
+          <t>0,0; 3,12</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 1,45</t>
+          <t>-5,19; 0,91</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 1,99</t>
+          <t>-3,76; 2,19</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,39</t>
+          <t>0,0; 9,2</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-88,72; 336,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0,56</t>
+          <t>0,23</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-30,69%</t>
+          <t>12,62%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,37; -0,16</t>
+          <t>-1,37; -0,13</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,58; -0,7</t>
+          <t>-2,62; -0,69</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 0,46</t>
+          <t>-1,56; 0,33</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 0,57</t>
+          <t>-0,85; 1,48</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 8,53</t>
+          <t>-91,84; 7,05</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-85,26; -27,96</t>
+          <t>-87,74; -28,26</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-64,18; 29,95</t>
+          <t>-65,18; 23,07</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-68,59; 40,44</t>
+          <t>-42,57; 97,34</t>
         </is>
       </c>
     </row>
